--- a/timetable_generator/timetable_outputs/CSE_Sem5_SectionB_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/CSE_Sem5_SectionB_Timetable.xlsx
@@ -468,10 +468,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CS303
-Computer networks 
-C101
-Dr. Dibyajyothi</t>
+          <t xml:space="preserve">CS309
+Statistics for computer science
+C101
+Dr. Pavan </t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -485,14 +485,7 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CS304
-Artificial intelligence
-C101
-Dr. Girish</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>CS303
@@ -502,7 +495,14 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CS303
+Computer networks 
+C101
+Dr. Dibyajyothi</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -511,22 +511,22 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CS304
+Artificial intelligence
+C101
+Dr. Girish</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">CS309
 Statistics for computer science
 C101
 Dr. Pavan </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CS303
-Computer networks 
-C101
-Dr. Dibyajyothi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -540,26 +540,20 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CS309
-Statistics for computer science
-C101
-Dr. Pavan </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>CS304
+Artificial intelligence
+C101
+Dr. Girish</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>CS303
 Computer networks 
 C101
-Dr. Dibyajyothi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CS304
-Artificial intelligence
-C101
-Dr. Girish</t>
+Dr. Dibyajyothi
+[TUTORIAL]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -570,24 +564,33 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CS309
-Statistics for computer science
-C101
-Dr. Pavan </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>CS304
 Artificial intelligence
 C101
-Dr. Girish</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+Dr. Girish
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CS303
+Computer networks 
+C101
+Dr. Dibyajyothi</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CS309
+Statistics for computer science
+C101
+Dr. Pavan 
+[TUTORIAL]</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
